--- a/data/trans_orig/P20B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P20B-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2007</t>
+          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2007 (tasa de respuesta: 99,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9716</t>
+          <t>9705</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17665</t>
+          <t>17930</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10795</t>
+          <t>10811</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23799</t>
+          <t>24254</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,66%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7541</t>
+          <t>7552</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14473</t>
+          <t>15263</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29477</t>
+          <t>29212</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40922</t>
+          <t>40885</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40600</t>
+          <t>40145</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53604</t>
+          <t>53588</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,21%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13588</t>
+          <t>13059</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16654</t>
+          <t>17350</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11109</t>
+          <t>10973</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26815</t>
+          <t>26544</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23695</t>
+          <t>24224</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33411</t>
+          <t>33533</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58657</t>
+          <t>57961</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>70260</t>
+          <t>70248</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>85779</t>
+          <t>86050</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>101485</t>
+          <t>101621</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,25%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>4017</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15001</t>
+          <t>14156</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11212</t>
+          <t>10489</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24283</t>
+          <t>24429</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18082</t>
+          <t>17302</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35054</t>
+          <t>33929</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>35,53%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22863</t>
+          <t>23708</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33925</t>
+          <t>33847</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33355</t>
+          <t>33209</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46426</t>
+          <t>47149</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60448</t>
+          <t>61573</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>77420</t>
+          <t>78200</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,88%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7721</t>
+          <t>7815</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19124</t>
+          <t>19244</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6348</t>
+          <t>6482</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20443</t>
+          <t>19025</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17091</t>
+          <t>17392</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33326</t>
+          <t>33912</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,87%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22454</t>
+          <t>22334</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33857</t>
+          <t>33763</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47833</t>
+          <t>49251</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61928</t>
+          <t>61794</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>76528</t>
+          <t>75942</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>92763</t>
+          <t>92462</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,17%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25274</t>
+          <t>26122</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45688</t>
+          <t>45854</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38941</t>
+          <t>36755</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62932</t>
+          <t>62079</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69951</t>
+          <t>71546</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102057</t>
+          <t>102438</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,79%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88294</t>
+          <t>88128</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>108708</t>
+          <t>107860</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>185435</t>
+          <t>186288</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>209426</t>
+          <t>211612</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>280292</t>
+          <t>279911</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>312398</t>
+          <t>310803</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,29%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2012</t>
+          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2012 (tasa de respuesta: 99,21%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8437</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21547</t>
+          <t>21599</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12110</t>
+          <t>12057</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27574</t>
+          <t>27105</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24388</t>
+          <t>24872</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43920</t>
+          <t>43582</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,36%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23841</t>
+          <t>23789</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36951</t>
+          <t>37081</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46912</t>
+          <t>47381</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62376</t>
+          <t>62429</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>75954</t>
+          <t>76292</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>95486</t>
+          <t>95002</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,25%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23571</t>
+          <t>23860</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17688</t>
+          <t>18132</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36383</t>
+          <t>36476</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31380</t>
+          <t>32287</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55882</t>
+          <t>55360</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,06%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38006</t>
+          <t>37717</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52111</t>
+          <t>52748</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>59949</t>
+          <t>59856</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>78644</t>
+          <t>78200</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>102027</t>
+          <t>102549</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>126529</t>
+          <t>125622</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>79,55%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9881</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24969</t>
+          <t>25199</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10491</t>
+          <t>10585</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26280</t>
+          <t>26216</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24100</t>
+          <t>23334</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46620</t>
+          <t>46098</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,43%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22744</t>
+          <t>22514</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37832</t>
+          <t>37808</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49180</t>
+          <t>49244</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64969</t>
+          <t>64875</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>76553</t>
+          <t>77075</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>99073</t>
+          <t>99839</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>81,06%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8843</t>
+          <t>9228</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22442</t>
+          <t>22397</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11876</t>
+          <t>12198</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26750</t>
+          <t>27699</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24878</t>
+          <t>24562</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45539</t>
+          <t>45032</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>31,86%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30645</t>
+          <t>30690</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44244</t>
+          <t>43859</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61507</t>
+          <t>60558</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76381</t>
+          <t>76059</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>95805</t>
+          <t>96312</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>116466</t>
+          <t>116782</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,62%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48081</t>
+          <t>49306</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78523</t>
+          <t>78396</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>66124</t>
+          <t>66734</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>98443</t>
+          <t>98841</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>125411</t>
+          <t>122540</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>166042</t>
+          <t>167472</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,88%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>129242</t>
+          <t>129369</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>159684</t>
+          <t>158459</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>236093</t>
+          <t>235695</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>268412</t>
+          <t>267802</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>376259</t>
+          <t>374829</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>416890</t>
+          <t>419761</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>77,4%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2016</t>
+          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2016 (tasa de respuesta: 98,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12746</t>
+          <t>12545</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24117</t>
+          <t>24107</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7910</t>
+          <t>8041</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20643</t>
+          <t>21433</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23253</t>
+          <t>23524</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40816</t>
+          <t>41609</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>50,64%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11907</t>
+          <t>11917</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23278</t>
+          <t>23479</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25499</t>
+          <t>24709</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38232</t>
+          <t>38101</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41351</t>
+          <t>40558</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58914</t>
+          <t>58643</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,37%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7031</t>
+          <t>6529</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18937</t>
+          <t>18556</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9406</t>
+          <t>9104</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24046</t>
+          <t>23716</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18684</t>
+          <t>19455</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38090</t>
+          <t>37612</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,66%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26742</t>
+          <t>27123</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38648</t>
+          <t>39150</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52962</t>
+          <t>53292</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>67602</t>
+          <t>67904</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>84596</t>
+          <t>85074</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>104002</t>
+          <t>103231</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,14%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5998</t>
+          <t>6038</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18058</t>
+          <t>18586</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7913</t>
+          <t>7725</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21534</t>
+          <t>21743</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17159</t>
+          <t>17100</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34329</t>
+          <t>34655</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,92%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15135</t>
+          <t>14607</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27195</t>
+          <t>27155</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34311</t>
+          <t>34102</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47932</t>
+          <t>48120</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54709</t>
+          <t>54383</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>71879</t>
+          <t>71938</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,79%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7764</t>
+          <t>7412</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20089</t>
+          <t>19284</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13926</t>
+          <t>14327</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32123</t>
+          <t>31335</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25825</t>
+          <t>24911</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47900</t>
+          <t>47025</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,05%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27492</t>
+          <t>28297</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39817</t>
+          <t>40169</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>58413</t>
+          <t>59201</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76610</t>
+          <t>76209</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>90217</t>
+          <t>91092</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>112292</t>
+          <t>113206</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,96%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42502</t>
+          <t>41819</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66360</t>
+          <t>67203</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51703</t>
+          <t>50800</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79847</t>
+          <t>81415</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>101246</t>
+          <t>102423</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>140920</t>
+          <t>142450</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,97%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>96117</t>
+          <t>95274</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>119975</t>
+          <t>120658</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>189684</t>
+          <t>188116</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>217828</t>
+          <t>218731</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>291088</t>
+          <t>289558</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>330762</t>
+          <t>329585</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,29%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2023</t>
+          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10454</t>
+          <t>11138</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22700</t>
+          <t>23393</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7352</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16951</t>
+          <t>17757</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19926</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36146</t>
+          <t>36580</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>42,27%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21650</t>
+          <t>20957</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33896</t>
+          <t>33212</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25246</t>
+          <t>24440</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34845</t>
+          <t>35037</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50401</t>
+          <t>49967</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66621</t>
+          <t>66876</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,27%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6623</t>
+          <t>6992</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18895</t>
+          <t>18401</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7972</t>
+          <t>8543</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21667</t>
+          <t>24658</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17872</t>
+          <t>18467</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36316</t>
+          <t>36614</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>33,03%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28593</t>
+          <t>29087</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40865</t>
+          <t>40496</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>41685</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55380</t>
+          <t>54809</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>74524</t>
+          <t>74226</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>92968</t>
+          <t>92373</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,34%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8238</t>
+          <t>8757</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19810</t>
+          <t>20301</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3821</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>11345</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14294</t>
+          <t>14220</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29573</t>
+          <t>29076</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,18%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15579</t>
+          <t>15088</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27151</t>
+          <t>26632</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26978</t>
+          <t>27483</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35007</t>
+          <t>35096</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>44644</t>
+          <t>45141</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59923</t>
+          <t>59997</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,84%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13837</t>
+          <t>13925</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26394</t>
+          <t>27015</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12237</t>
+          <t>12006</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24303</t>
+          <t>23585</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28710</t>
+          <t>28446</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47093</t>
+          <t>46140</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>34,61%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34437</t>
+          <t>33816</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>46994</t>
+          <t>46906</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48164</t>
+          <t>48882</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60230</t>
+          <t>60461</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>86205</t>
+          <t>87158</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>104588</t>
+          <t>104852</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,66%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49639</t>
+          <t>50441</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74594</t>
+          <t>74818</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39667</t>
+          <t>40092</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60527</t>
+          <t>61718</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>95101</t>
+          <t>96172</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>129204</t>
+          <t>129947</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,09%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>113464</t>
+          <t>113240</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>138419</t>
+          <t>137617</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>156316</t>
+          <t>155125</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>177176</t>
+          <t>176751</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>275698</t>
+          <t>274955</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>309801</t>
+          <t>308730</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,25%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P20B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P20B-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9705</t>
+          <t>9676</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6183</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17930</t>
+          <t>18136</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>10993</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24254</t>
+          <t>24109</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,44%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7552</t>
+          <t>7581</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15263</t>
+          <t>15273</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29212</t>
+          <t>29006</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40885</t>
+          <t>40959</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40145</t>
+          <t>40290</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53588</t>
+          <t>53406</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>82,93%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>3749</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13059</t>
+          <t>13939</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>5376</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17350</t>
+          <t>18333</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10973</t>
+          <t>11161</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26544</t>
+          <t>26822</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24224</t>
+          <t>23344</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33533</t>
+          <t>33534</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>57961</t>
+          <t>56978</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>70248</t>
+          <t>69935</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>86050</t>
+          <t>85772</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>101621</t>
+          <t>101433</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,09%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14156</t>
+          <t>15073</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10489</t>
+          <t>11019</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24429</t>
+          <t>24417</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17302</t>
+          <t>16795</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33929</t>
+          <t>34600</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>36,23%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23708</t>
+          <t>22791</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33847</t>
+          <t>33795</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33209</t>
+          <t>33221</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47149</t>
+          <t>46619</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61573</t>
+          <t>60902</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>78200</t>
+          <t>78707</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>82,41%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7815</t>
+          <t>7753</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19244</t>
+          <t>18663</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6482</t>
+          <t>6904</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19025</t>
+          <t>20529</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17392</t>
+          <t>17505</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33912</t>
+          <t>35248</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>32,09%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22334</t>
+          <t>22915</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33763</t>
+          <t>33825</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49251</t>
+          <t>47747</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61794</t>
+          <t>61372</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>75942</t>
+          <t>74606</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>92462</t>
+          <t>92349</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,07%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26122</t>
+          <t>26457</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45854</t>
+          <t>45426</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36755</t>
+          <t>38624</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62079</t>
+          <t>63528</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71546</t>
+          <t>70362</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102438</t>
+          <t>102503</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88128</t>
+          <t>88556</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>107860</t>
+          <t>107525</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>186288</t>
+          <t>184839</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>211612</t>
+          <t>209743</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>279911</t>
+          <t>279846</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>310803</t>
+          <t>311987</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,6%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8307</t>
+          <t>9480</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21599</t>
+          <t>21919</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12057</t>
+          <t>12171</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27105</t>
+          <t>27315</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24872</t>
+          <t>24153</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43582</t>
+          <t>43155</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,0%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23789</t>
+          <t>23469</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37081</t>
+          <t>35908</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47381</t>
+          <t>47171</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62429</t>
+          <t>62315</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>76292</t>
+          <t>76719</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>95002</t>
+          <t>95721</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,85%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>9356</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23860</t>
+          <t>23387</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18132</t>
+          <t>17841</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36476</t>
+          <t>36323</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32287</t>
+          <t>31609</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55360</t>
+          <t>55416</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,09%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37717</t>
+          <t>38190</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52748</t>
+          <t>52221</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>59856</t>
+          <t>60009</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>78200</t>
+          <t>78491</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>102549</t>
+          <t>102493</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>125622</t>
+          <t>126300</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9905</t>
+          <t>9427</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25199</t>
+          <t>24120</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10585</t>
+          <t>10488</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26216</t>
+          <t>25626</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23334</t>
+          <t>23124</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46098</t>
+          <t>43869</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>35,62%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22514</t>
+          <t>23593</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37808</t>
+          <t>38286</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49244</t>
+          <t>49834</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64875</t>
+          <t>64972</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>77075</t>
+          <t>79304</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>99839</t>
+          <t>100049</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,23%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>8836</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22397</t>
+          <t>21689</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12198</t>
+          <t>12349</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27699</t>
+          <t>27524</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24562</t>
+          <t>25370</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45032</t>
+          <t>46409</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,83%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30690</t>
+          <t>31398</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43859</t>
+          <t>44251</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60558</t>
+          <t>60733</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76059</t>
+          <t>75908</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>96312</t>
+          <t>94935</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>116782</t>
+          <t>115974</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,05%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49306</t>
+          <t>48660</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78396</t>
+          <t>77457</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>66734</t>
+          <t>67275</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>98841</t>
+          <t>99595</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>122540</t>
+          <t>125932</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>167472</t>
+          <t>166310</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>129369</t>
+          <t>130308</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>158459</t>
+          <t>159105</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>235695</t>
+          <t>234941</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>267802</t>
+          <t>267261</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>374829</t>
+          <t>375991</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>419761</t>
+          <t>416369</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>76,78%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12545</t>
+          <t>12050</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24107</t>
+          <t>23775</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8041</t>
+          <t>7959</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21433</t>
+          <t>20836</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23524</t>
+          <t>23030</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41609</t>
+          <t>40972</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>49,86%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11917</t>
+          <t>12249</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23479</t>
+          <t>23974</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24709</t>
+          <t>25306</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38101</t>
+          <t>38183</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40558</t>
+          <t>41195</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58643</t>
+          <t>59137</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,97%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>6771</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18556</t>
+          <t>19208</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9104</t>
+          <t>8595</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23716</t>
+          <t>23906</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19455</t>
+          <t>19172</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37612</t>
+          <t>39659</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>32,33%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27123</t>
+          <t>26471</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39150</t>
+          <t>38908</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53292</t>
+          <t>53102</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>67904</t>
+          <t>68413</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>85074</t>
+          <t>83027</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>103231</t>
+          <t>103514</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,37%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6038</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18586</t>
+          <t>18770</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7725</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21743</t>
+          <t>21293</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17100</t>
+          <t>16455</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34655</t>
+          <t>35281</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>39,62%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14607</t>
+          <t>14423</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27155</t>
+          <t>27116</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34102</t>
+          <t>34552</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48120</t>
+          <t>47947</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54383</t>
+          <t>53757</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>71938</t>
+          <t>72583</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>81,52%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7412</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19284</t>
+          <t>20162</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14327</t>
+          <t>13716</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31335</t>
+          <t>31701</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24911</t>
+          <t>25276</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47025</t>
+          <t>47028</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28297</t>
+          <t>27419</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40169</t>
+          <t>39498</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59201</t>
+          <t>58835</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76209</t>
+          <t>76820</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>91092</t>
+          <t>91089</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>113206</t>
+          <t>112841</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,7%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41819</t>
+          <t>43294</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>67203</t>
+          <t>68491</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50800</t>
+          <t>52809</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>81415</t>
+          <t>81571</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>102423</t>
+          <t>101805</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>142450</t>
+          <t>140282</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>95274</t>
+          <t>93986</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>120658</t>
+          <t>119183</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>188116</t>
+          <t>187960</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>218731</t>
+          <t>216722</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>289558</t>
+          <t>291726</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>329585</t>
+          <t>330203</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,43%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>15997</t>
+          <t>16651</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11138</t>
+          <t>10937</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23393</t>
+          <t>23726</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11551</t>
+          <t>13319</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>8562</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17757</t>
+          <t>19452</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>27548</t>
+          <t>29970</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19671</t>
+          <t>22160</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36580</t>
+          <t>39562</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>41,72%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28353</t>
+          <t>31270</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20957</t>
+          <t>24195</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33212</t>
+          <t>36984</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30646</t>
+          <t>33580</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24440</t>
+          <t>27447</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35037</t>
+          <t>38337</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>58999</t>
+          <t>64849</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49967</t>
+          <t>55257</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66876</t>
+          <t>72659</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>76,63%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>44350</t>
+          <t>47921</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44350</t>
+          <t>47921</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44350</t>
+          <t>47921</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>42197</t>
+          <t>46899</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>42197</t>
+          <t>46899</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42197</t>
+          <t>46899</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>86547</t>
+          <t>94819</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>86547</t>
+          <t>94819</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>86547</t>
+          <t>94819</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12287</t>
+          <t>15652</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6992</t>
+          <t>9529</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18401</t>
+          <t>24640</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13841</t>
+          <t>15453</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8543</t>
+          <t>9734</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24658</t>
+          <t>25326</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>26128</t>
+          <t>31105</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18467</t>
+          <t>22081</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36614</t>
+          <t>44166</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>35201</t>
+          <t>38966</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29087</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40496</t>
+          <t>45089</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>49511</t>
+          <t>54258</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>44385</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>54809</t>
+          <t>59977</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>84712</t>
+          <t>93224</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>74226</t>
+          <t>80163</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>92373</t>
+          <t>102248</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>82,24%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47488</t>
+          <t>54618</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47488</t>
+          <t>54618</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47488</t>
+          <t>54618</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>63352</t>
+          <t>69711</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63352</t>
+          <t>69711</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63352</t>
+          <t>69711</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>110840</t>
+          <t>124329</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>110840</t>
+          <t>124329</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>110840</t>
+          <t>124329</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14195</t>
+          <t>15451</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8757</t>
+          <t>9554</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20301</t>
+          <t>22170</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>9184</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3732</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11345</t>
+          <t>14187</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>21169</t>
+          <t>24635</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14220</t>
+          <t>17234</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29076</t>
+          <t>33877</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>38,59%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21194</t>
+          <t>22591</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15088</t>
+          <t>15872</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26632</t>
+          <t>28488</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31853</t>
+          <t>40564</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27483</t>
+          <t>35561</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35096</t>
+          <t>44423</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>53048</t>
+          <t>63155</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>45141</t>
+          <t>53913</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59997</t>
+          <t>70556</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,37%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35389</t>
+          <t>38042</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35389</t>
+          <t>38042</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35389</t>
+          <t>38042</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>38828</t>
+          <t>49748</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38828</t>
+          <t>49748</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38828</t>
+          <t>49748</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>74217</t>
+          <t>87790</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>74217</t>
+          <t>87790</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>74217</t>
+          <t>87790</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19798</t>
+          <t>20448</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13925</t>
+          <t>14242</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27015</t>
+          <t>27789</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17477</t>
+          <t>19330</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12006</t>
+          <t>13462</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23585</t>
+          <t>25783</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>37275</t>
+          <t>39777</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28446</t>
+          <t>31447</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46140</t>
+          <t>48729</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>33,91%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>41033</t>
+          <t>44150</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33816</t>
+          <t>36809</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>46906</t>
+          <t>50356</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>54990</t>
+          <t>59780</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48882</t>
+          <t>53327</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60461</t>
+          <t>65648</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>96023</t>
+          <t>103931</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>87158</t>
+          <t>94979</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>104852</t>
+          <t>112261</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,12%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>60831</t>
+          <t>64598</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>60831</t>
+          <t>64598</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>60831</t>
+          <t>64598</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>72467</t>
+          <t>79110</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>72467</t>
+          <t>79110</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>72467</t>
+          <t>79110</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>133298</t>
+          <t>143708</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>133298</t>
+          <t>143708</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>133298</t>
+          <t>143708</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>62276</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50441</t>
+          <t>54867</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74818</t>
+          <t>81090</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40092</t>
+          <t>45331</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61718</t>
+          <t>71653</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>112120</t>
+          <t>125487</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>96172</t>
+          <t>108858</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>129947</t>
+          <t>144554</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,08%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>125782</t>
+          <t>136976</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>113240</t>
+          <t>124088</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>137617</t>
+          <t>150311</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>167000</t>
+          <t>188182</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>155125</t>
+          <t>173814</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>176751</t>
+          <t>200136</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>292782</t>
+          <t>325158</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>274955</t>
+          <t>306091</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>308730</t>
+          <t>341787</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>75,84%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>188058</t>
+          <t>205178</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>188058</t>
+          <t>205178</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>188058</t>
+          <t>205178</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>216843</t>
+          <t>245467</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>216843</t>
+          <t>245467</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>216843</t>
+          <t>245467</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>404902</t>
+          <t>450645</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>404902</t>
+          <t>450645</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>404902</t>
+          <t>450645</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
